--- a/excel/20260805_タイムレコード_使い方.xlsx
+++ b/excel/20260805_タイムレコード_使い方.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>■ 1. 3つのファイルの使い分け</t>
+          <t>■ 1. ファイルの使い分け</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>画面を操作して実測値を出す</t>
+          <t>画面を操作して実測値を出す。「ヘルプ該当箇所」列に、仕様が変わったとき直すヘルプの節が書いてある</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -544,180 +544,180 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>03_検証用データセット.xlsx</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>検証に使うデータを用意する（前提データD0／CSVに入力する値D1〜D5）</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>記入しない。読むだけ</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>ヘルプページ.xlsx</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>顧客向けヘルプの本文・フロー図・公開手順を確認する</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>掲載前チェックのみ記入</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>■ 2. 使う順番</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>使うファイル</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>実装前：MVP必須44件をエンジニアと合意する</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>01（E列＝MVP必須で絞る）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>実装後：エンジニアが実装状況を確認する</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>検証：段階順に操作して実測値を出す</t>
+          <t>実装前：MVP必須45件をエンジニアと合意する</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01（E列＝MVP必須で絞る）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>判定：実測値が合格ラインを満たすか判断する</t>
+          <t>実装後：エンジニアが実装状況を確認する</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>01（N列に OK/NG）</t>
+          <t>01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>検証：段階順に操作して実測値を出す</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>判定：実測値が合格ラインを満たすか判断する</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>01（N列に OK/NG）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>※</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>受入条件は2回使う。実装前は「約束」、実装後は「判定」</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>■ 3. 受入条件表の画面構造</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>行</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>操作</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>4〜12行</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>到達状況：マイルストーン別（M1〜M6＋対象外）</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>自動計算。触らない</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>13行</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>総合判定</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>自動計算。触らない</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>15〜19行</t>
+          <t>4〜12行</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>到達状況：フロー別（1〜4）</t>
+          <t>到達状況：マイルストーン別（M1〜M6＋対象外）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -729,102 +729,110 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
+          <t>13行</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>総合判定</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>自動計算。触らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>15〜19行</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>到達状況：フロー別（1〜4）</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>自動計算。触らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>21〜25行</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>到達状況：実装レベル別</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>自動計算。触らない</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>28行</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>見出し（オートフィルタ付き）</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>絞り込みに使う</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>29〜116行</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>受入条件88件</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>ここに記入する（N列の合否）</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>N列「合否」のプルダウンから OK / NG / 対象外 を選ぶ</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>O列「実測値」に測った数値、P列「判定者」、Q列「判定日」を入れる</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>上部の到達表と総合判定が自動で更新される</t>
+          <t>N列「合否」のプルダウンから OK / NG / 対象外 を選ぶ</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -832,467 +840,471 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>O列「実測値」に測った数値、P列「判定者」、Q列「判定日」を入れる</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>上部の到達表と総合判定が自動で更新される</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>※</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>黄色いセルが記入欄。それ以外は編集しない</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>■ 5. 列の意味（88条件の各行）</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>列</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>名前</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>何が書いてあるか</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>A・B</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>マイルストーン／完了条件</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>実装順のグループ（M1〜M6）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>設計ポイント</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>①データを壊さない 〜 ⑬検証の前提 のまとまり</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A・B</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>条件ID</t>
+          <t>マイルストーン／完了条件</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>AC-001〜</t>
+          <t>実装順のグループ（M1〜M6）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>実装レベル</t>
+          <t>設計ポイント</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>MVP必須（赤）／リリース必須（黄）／改善（青）／対象外（灰）</t>
+          <t>①データを壊さない 〜 ⑬検証の前提 のまとまり</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>何を実装するか</t>
+          <t>条件ID</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>作るもの</t>
+          <t>AC-001〜</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>合格ライン</t>
+          <t>実装レベル</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>どこまでできたら完了か。すべて数値で書いてある</t>
+          <t>MVP必須（赤）／リリース必須（黄）／改善（青）／対象外（灰）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>実装できていないと起きること</t>
+          <t>何を実装するか</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>なぜ必要かの理由。実装の優先度はここで判断する</t>
+          <t>作るもの</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>フロー</t>
+          <t>合格ライン</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1 新規登録（手入力）／2 新規登録（CSV）／3 運用（手入力）／4 運用（CSV）</t>
+          <t>どこまでできたら完了か。すべて数値で書いてある</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>確認する画面</t>
+          <t>実装できていないと起きること</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>判定するときに開く画面</t>
+          <t>なぜ必要かの理由。実装の優先度はここで判断する</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>確認方法</t>
+          <t>フロー</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>動作確認／動作確認＋DB確認／実装レビュー</t>
+          <t>1 新規登録（手入力）／2 新規登録（CSV）／3 運用（手入力）／4 運用（CSV）</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>仕様書の根拠</t>
+          <t>確認する画面</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>仕様書の該当章</t>
+          <t>判定するときに開く画面</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>対応検証ID</t>
+          <t>確認方法</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>検証プランの該当ケース</t>
+          <t>動作確認／動作確認＋DB確認／実装レビュー</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>仕様書の根拠</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>仕様書の該当章</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>対応検証ID</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>検証プランの該当ケース</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>N〜Q</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>合否／実測値／判定者／判定日</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>記入欄（黄色）</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>■ 6. 読む順番</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>誰が</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>どう読むか</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>エンジニア（実装前）</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>E列がMVP必須の行から着手。上から順（M1→M6）に実装すれば依存関係どおりに進む。各行で F・G・H を見る</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>判定する人（実装後）</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>J列の画面を開き、G列の合格ラインと突き合わせて N列に OK/NG を入れる</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>エンジニア（実装前）</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>E列がMVP必須の行から着手。上から順（M1→M6）に実装すれば依存関係どおりに進む。各行で F・G・H を見る</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>判定する人（実装後）</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>J列の画面を開き、G列の合格ラインと突き合わせて N列に OK/NG を入れる</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>根拠を辿りたいとき</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>L列で仕様書へ、M列で検証プランへ飛べる</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>■ 7. 到達表の見方（上部）</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>次にすること</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>到達率100%</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>そのマイルストーンは全条件OK</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>次のマイルストーンへ</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>未判定が残る</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>まだ判定していない条件がある</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>残りを判定する</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>NGあり</t>
+          <t>到達率100%</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>落ちている条件がある</t>
+          <t>そのマイルストーンは全条件OK</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>NGの行を見て対応を決める</t>
+          <t>次のマイルストーンへ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>総合判定（12行）</t>
+          <t>未判定が残る</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
+          <t>まだ判定していない条件がある</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>残りを判定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>NGあり</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>落ちている条件がある</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>NGの行を見て対応を決める</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>総合判定（13行）</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
           <t>MVP必須にNGがあれば「リリース不可」、全部OKなら「リリース可」</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>最終結論はここ</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>■ 8. よく使う絞り込み（17行のフィルタ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="61"/>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>■ 8. よく使う絞り込み（28行のフィルタ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>絞り込み</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>目的</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="inlineStr">
-        <is>
-          <t>E列＝MVP必須</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>最低限やることだけ見る</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>I列＝1</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>手入力での新規登録（セルフスタート）だけ見る</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>I列＝2</t>
+          <t>E列＝MVP必須</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>CSVインポートでの新規登録だけ見る</t>
+          <t>最低限やることだけ見る</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -1300,12 +1312,12 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>K列＝実装レビュー</t>
+          <t>I列＝1</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>動作では確認できない条件だけ見る（成果物を開いて判断する）</t>
+          <t>手入力での新規登録（セルフスタート）だけ見る</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -1313,71 +1325,72 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
+          <t>I列＝2</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>CSVインポートでの新規登録だけ見る</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>K列＝実装レビュー</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>動作では確認できない条件だけ見る（成果物を開いて判断する）</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
           <t>N列＝NG</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>落ちている条件だけ見る</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>■ 9. 注意点</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>確認方法が「実装レビュー」</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>動かしても確認できない。配布テンプレートの列やスキーマの一致は、成果物そのものを開いて突き合わせる</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>一部だけ満たしている</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>合格ラインは「〜＝0件」の形。部分的な達成は NG。実測値に何が足りないかを書く</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>1つの検証が複数条件の根拠</t>
+          <t>確認方法が「実装レビュー」</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>検証は1回、判定は条件ごと。例：OP-503 は AC-043・AC-044・AC-046 の根拠</t>
+          <t>動かしても確認できない。配布テンプレートの列やスキーマの一致は、成果物そのものを開いて突き合わせる</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -1385,61 +1398,88 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
+          <t>一部だけ満たしている</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>合格ラインは「〜＝0件」の形。部分的な達成は NG。実測値に何が足りないかを書く</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>1つの検証が複数条件の根拠</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>検証は1回、判定は条件ごと。例：OP-503 は AC-043・AC-044・AC-046 の根拠</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
           <t>合格ラインが実装と食い違う</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>実装を直すのが原則。仕様の誤りなら定義表と仕様書の両方を直す</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>■ 10. 画面モック</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>経路</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>URL</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>手入力（登録・編集・削除／初期セットアップ・設定画面）</t>
         </is>
       </c>
-      <c r="B77" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>https://suguru789987.github.io/rakmy-owner-registration-mock/</t>
         </is>
       </c>
-      <c r="C77" s="4" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>CSVインポート</t>
         </is>
       </c>
-      <c r="B78" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>https://suguru789987.github.io/rakmy-timerecord-import-spec/</t>
         </is>
       </c>
-      <c r="C78" s="4" t="inlineStr"/>
+      <c r="C80" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/20260805_タイムレコード_使い方.xlsx
+++ b/excel/20260805_タイムレコード_使い方.xlsx
@@ -468,7 +468,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -578,7 +577,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -667,7 +665,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>01（N列に OK/NG）</t>
+          <t>01（O列に OK/NG）</t>
         </is>
       </c>
     </row>
@@ -684,7 +682,6 @@
       </c>
       <c r="C17" s="4" t="inlineStr"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -807,7 +804,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ここに記入する（N列の合否）</t>
+          <t>ここに記入する（O列の合否）</t>
         </is>
       </c>
     </row>
@@ -832,7 +829,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>N列「合否」のプルダウンから OK / NG / 対象外 を選ぶ</t>
+          <t>O列「合否」のプルダウンから OK / NG / 対象外 を選ぶ</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -845,7 +842,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>O列「実測値」に測った数値、P列「判定者」、Q列「判定日」を入れる</t>
+          <t>P列「実測値」に測った数値、Q列「判定者」、R列「判定日」を入れる</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -876,7 +873,6 @@
       </c>
       <c r="C31" s="4" t="inlineStr"/>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -1091,24 +1087,24 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>M・N</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>対応検証ID</t>
+          <t>対応検証ID／ヘルプ該当箇所</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>検証プランの該当ケース</t>
+          <t>検証プランの該当ケースと、仕様が変わったとき直すヘルプの節</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>N〜Q</t>
+          <t>O〜R</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
@@ -1164,7 +1160,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>J列の画面を開き、G列の合格ラインと突き合わせて N列に OK/NG を入れる</t>
+          <t>J列の画面を開き、G列の合格ラインと突き合わせて O列に OK/NG を入れる</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -1177,12 +1173,11 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>L列で仕様書へ、M列で検証プランへ飛べる</t>
+          <t>L列で仕様書へ、M列で検証プランへ、N列でヘルプページへ飛べる</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
@@ -1275,7 +1270,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
@@ -1351,7 +1345,7 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>N列＝NG</t>
+          <t>O列＝NG</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -1361,7 +1355,6 @@
       </c>
       <c r="C68" s="4" t="inlineStr"/>
     </row>
-    <row r="69"/>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
@@ -1434,7 +1427,6 @@
       </c>
       <c r="C75" s="4" t="inlineStr"/>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>

--- a/excel/20260805_タイムレコード_使い方.xlsx
+++ b/excel/20260805_タイムレコード_使い方.xlsx
@@ -468,6 +468,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -577,6 +578,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -682,6 +684,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -873,6 +876,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr"/>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
@@ -1178,6 +1182,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr"/>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
@@ -1270,6 +1275,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
@@ -1355,6 +1361,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr"/>
     </row>
+    <row r="69"/>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
@@ -1427,6 +1434,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr"/>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
